--- a/excel_templates/wzor_import_hu_kontrola.xlsx
+++ b/excel_templates/wzor_import_hu_kontrola.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kompres 10x10</t>
+          <t>Kubek 10x10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Szpital Przykładowy</t>
+          <t>Sklep Przykładowy</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rękawice L</t>
+          <t>Talerze L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Szpital Przykładowy</t>
+          <t>Sklep Przykładowy</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kompres 10x10</t>
+          <t>Kubek 10x10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Klinika Demo</t>
+          <t>Hurtownia Demo</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
